--- a/data/output/escala_final.xlsx
+++ b/data/output/escala_final.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG28"/>
+  <dimension ref="A1:AF28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -527,11 +527,6 @@
       <c r="AF1" s="1" t="n">
         <v>31</v>
       </c>
-      <c r="AG1" s="1" t="inlineStr">
-        <is>
-          <t>TOTAL 12 HORAS</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -542,16 +537,16 @@
       <c r="B2" t="n">
         <v>0</v>
       </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="C2" t="n">
+        <v>0</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
-      <c r="E2" t="n">
-        <v>0</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -562,16 +557,16 @@
       <c r="H2" t="n">
         <v>0</v>
       </c>
-      <c r="I2" t="n">
-        <v>0</v>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="J2" t="n">
         <v>0</v>
       </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="K2" t="n">
+        <v>0</v>
       </c>
       <c r="L2" t="n">
         <v>0</v>
@@ -582,8 +577,10 @@
       <c r="N2" t="n">
         <v>0</v>
       </c>
-      <c r="O2" t="n">
-        <v>0</v>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="P2" t="n">
         <v>0</v>
@@ -597,14 +594,12 @@
       <c r="S2" t="n">
         <v>0</v>
       </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="T2" t="n">
+        <v>0</v>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="V2" t="n">
@@ -622,13 +617,13 @@
       <c r="Z2" t="n">
         <v>0</v>
       </c>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="AB2" t="n">
-        <v>0</v>
+      <c r="AA2" t="n">
+        <v>0</v>
+      </c>
+      <c r="AB2" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AC2" t="n">
         <v>0</v>
@@ -640,9 +635,6 @@
         <v>0</v>
       </c>
       <c r="AF2" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG2" t="n">
         <v>0</v>
       </c>
     </row>
@@ -661,19 +653,21 @@
       <c r="D3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="F3" t="n">
-        <v>0</v>
+      <c r="E3" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="H3" t="n">
-        <v>0</v>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="I3" t="n">
         <v>0</v>
@@ -684,10 +678,8 @@
       <c r="K3" t="n">
         <v>0</v>
       </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
+      <c r="L3" t="n">
+        <v>0</v>
       </c>
       <c r="M3" t="n">
         <v>0</v>
@@ -698,24 +690,22 @@
       <c r="O3" t="n">
         <v>0</v>
       </c>
-      <c r="P3" t="n">
-        <v>0</v>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="R3" t="n">
+        <v>0</v>
       </c>
       <c r="S3" t="n">
         <v>0</v>
       </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="T3" t="n">
+        <v>0</v>
       </c>
       <c r="U3" t="n">
         <v>0</v>
@@ -726,22 +716,24 @@
       <c r="W3" t="n">
         <v>0</v>
       </c>
-      <c r="X3" t="n">
-        <v>0</v>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="Y3" t="n">
         <v>0</v>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="Z3" t="n">
+        <v>0</v>
       </c>
       <c r="AA3" t="n">
         <v>0</v>
       </c>
-      <c r="AB3" t="n">
-        <v>0</v>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AC3" t="n">
         <v>0</v>
@@ -753,9 +745,6 @@
         <v>0</v>
       </c>
       <c r="AF3" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG3" t="n">
         <v>0</v>
       </c>
     </row>
@@ -776,7 +765,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -788,13 +777,13 @@
       <c r="H4" t="n">
         <v>0</v>
       </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="J4" t="n">
-        <v>0</v>
+      <c r="I4" t="n">
+        <v>0</v>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="K4" t="n">
         <v>0</v>
@@ -805,10 +794,8 @@
       <c r="M4" t="n">
         <v>0</v>
       </c>
-      <c r="N4" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="N4" t="n">
+        <v>0</v>
       </c>
       <c r="O4" t="n">
         <v>0</v>
@@ -819,8 +806,10 @@
       <c r="Q4" t="n">
         <v>0</v>
       </c>
-      <c r="R4" t="n">
-        <v>0</v>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="S4" t="n">
         <v>0</v>
@@ -828,28 +817,28 @@
       <c r="T4" t="n">
         <v>0</v>
       </c>
-      <c r="U4" t="inlineStr">
+      <c r="U4" t="n">
+        <v>0</v>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="W4" t="n">
+        <v>0</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z4" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="V4" t="n">
-        <v>0</v>
-      </c>
-      <c r="W4" t="n">
-        <v>0</v>
-      </c>
-      <c r="X4" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y4" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="Z4" t="n">
-        <v>0</v>
-      </c>
       <c r="AA4" t="n">
         <v>0</v>
       </c>
@@ -866,9 +855,6 @@
         <v>0</v>
       </c>
       <c r="AF4" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG4" t="n">
         <v>0</v>
       </c>
     </row>
@@ -878,8 +864,10 @@
           <t>PEDRO GUIDI PEREIRA</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>0</v>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="C5" t="n">
         <v>0</v>
@@ -887,10 +875,8 @@
       <c r="D5" t="n">
         <v>0</v>
       </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="E5" t="n">
+        <v>0</v>
       </c>
       <c r="F5" t="n">
         <v>0</v>
@@ -910,19 +896,21 @@
       <c r="K5" t="n">
         <v>0</v>
       </c>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="M5" t="n">
-        <v>0</v>
+      <c r="L5" t="n">
+        <v>0</v>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
       </c>
       <c r="N5" t="n">
         <v>0</v>
       </c>
-      <c r="O5" t="n">
-        <v>0</v>
+      <c r="O5" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="P5" t="n">
         <v>0</v>
@@ -933,21 +921,19 @@
       <c r="R5" t="n">
         <v>0</v>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
+      <c r="S5" t="n">
+        <v>0</v>
       </c>
       <c r="T5" t="n">
         <v>0</v>
       </c>
-      <c r="U5" t="n">
-        <v>0</v>
-      </c>
-      <c r="V5" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="V5" t="n">
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
@@ -975,15 +961,10 @@
       <c r="AD5" t="n">
         <v>0</v>
       </c>
-      <c r="AE5" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AE5" t="n">
+        <v>0</v>
       </c>
       <c r="AF5" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG5" t="n">
         <v>0</v>
       </c>
     </row>
@@ -993,10 +974,8 @@
           <t>ELIAS PIRES JUNIOR</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="B6" t="n">
+        <v>0</v>
       </c>
       <c r="C6" t="n">
         <v>0</v>
@@ -1007,8 +986,10 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" t="n">
-        <v>0</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
       </c>
       <c r="G6" t="n">
         <v>0</v>
@@ -1016,8 +997,10 @@
       <c r="H6" t="n">
         <v>0</v>
       </c>
-      <c r="I6" t="n">
-        <v>0</v>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="J6" t="n">
         <v>0</v>
@@ -1028,16 +1011,16 @@
       <c r="L6" t="n">
         <v>0</v>
       </c>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="M6" t="n">
+        <v>0</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
       </c>
-      <c r="O6" t="n">
-        <v>0</v>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="P6" t="n">
         <v>0</v>
@@ -1048,10 +1031,8 @@
       <c r="R6" t="n">
         <v>0</v>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
+      <c r="S6" t="n">
+        <v>0</v>
       </c>
       <c r="T6" t="n">
         <v>0</v>
@@ -1061,7 +1042,7 @@
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="W6" t="n">
@@ -1090,15 +1071,10 @@
       <c r="AD6" t="n">
         <v>0</v>
       </c>
-      <c r="AE6" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AE6" t="n">
+        <v>0</v>
       </c>
       <c r="AF6" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG6" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1117,13 +1093,13 @@
       <c r="D7" t="n">
         <v>0</v>
       </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
-      </c>
-      <c r="F7" t="n">
-        <v>0</v>
+      <c r="E7" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="G7" t="n">
         <v>0</v>
@@ -1131,10 +1107,8 @@
       <c r="H7" t="n">
         <v>0</v>
       </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="I7" t="n">
+        <v>0</v>
       </c>
       <c r="J7" t="n">
         <v>0</v>
@@ -1145,8 +1119,10 @@
       <c r="L7" t="n">
         <v>0</v>
       </c>
-      <c r="M7" t="n">
-        <v>0</v>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="N7" t="n">
         <v>0</v>
@@ -1160,16 +1136,18 @@
       <c r="Q7" t="n">
         <v>0</v>
       </c>
-      <c r="R7" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="S7" t="n">
-        <v>0</v>
-      </c>
-      <c r="T7" t="n">
-        <v>0</v>
+      <c r="R7" t="n">
+        <v>0</v>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="U7" t="n">
         <v>0</v>
@@ -1180,10 +1158,8 @@
       <c r="W7" t="n">
         <v>0</v>
       </c>
-      <c r="X7" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="X7" t="n">
+        <v>0</v>
       </c>
       <c r="Y7" t="n">
         <v>0</v>
@@ -1191,16 +1167,16 @@
       <c r="Z7" t="n">
         <v>0</v>
       </c>
-      <c r="AA7" t="n">
-        <v>0</v>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AB7" t="n">
         <v>0</v>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AC7" t="n">
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
         <v>0</v>
@@ -1209,9 +1185,6 @@
         <v>0</v>
       </c>
       <c r="AF7" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1221,10 +1194,8 @@
           <t>MAYA KURJAN CUNHA</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="B8" t="n">
+        <v>0</v>
       </c>
       <c r="C8" t="n">
         <v>0</v>
@@ -1235,8 +1206,10 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" t="n">
-        <v>0</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="G8" t="n">
         <v>0</v>
@@ -1284,13 +1257,13 @@
       <c r="T8" t="n">
         <v>0</v>
       </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="V8" t="n">
-        <v>0</v>
+      <c r="U8" t="n">
+        <v>0</v>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="W8" t="n">
         <v>0</v>
@@ -1303,7 +1276,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="AA8" t="n">
@@ -1318,15 +1291,12 @@
       <c r="AD8" t="n">
         <v>0</v>
       </c>
-      <c r="AE8" t="n">
-        <v>0</v>
-      </c>
-      <c r="AF8" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="AG8" t="n">
+      <c r="AE8" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="AF8" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1345,13 +1315,13 @@
       <c r="D9" t="n">
         <v>0</v>
       </c>
-      <c r="E9" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="F9" t="n">
+        <v>0</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
@@ -1362,8 +1332,10 @@
       <c r="I9" t="n">
         <v>0</v>
       </c>
-      <c r="J9" t="n">
-        <v>0</v>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="K9" t="n">
         <v>0</v>
@@ -1373,7 +1345,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="N9" t="n">
@@ -1391,44 +1363,42 @@
       <c r="R9" t="n">
         <v>0</v>
       </c>
-      <c r="S9" t="inlineStr">
+      <c r="S9" t="n">
+        <v>0</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="U9" t="n">
+        <v>0</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0</v>
+      </c>
+      <c r="X9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z9" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA9" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="T9" t="n">
-        <v>0</v>
-      </c>
-      <c r="U9" t="n">
-        <v>0</v>
-      </c>
-      <c r="V9" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="W9" t="n">
-        <v>0</v>
-      </c>
-      <c r="X9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y9" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA9" t="n">
-        <v>0</v>
-      </c>
       <c r="AB9" t="n">
         <v>0</v>
       </c>
-      <c r="AC9" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AC9" t="n">
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
@@ -1436,11 +1406,10 @@
       <c r="AE9" t="n">
         <v>0</v>
       </c>
-      <c r="AF9" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG9" t="n">
-        <v>0</v>
+      <c r="AF9" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
     </row>
     <row r="10">
@@ -1458,70 +1427,70 @@
       <c r="D10" t="n">
         <v>0</v>
       </c>
-      <c r="E10" t="inlineStr">
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="G10" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>0</v>
+      </c>
+      <c r="R10" t="n">
+        <v>0</v>
+      </c>
+      <c r="S10" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>0</v>
-      </c>
-      <c r="G10" t="n">
-        <v>0</v>
-      </c>
-      <c r="H10" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="J10" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="P10" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>0</v>
-      </c>
-      <c r="R10" t="n">
-        <v>0</v>
-      </c>
-      <c r="S10" t="n">
-        <v>0</v>
-      </c>
       <c r="T10" t="n">
         <v>0</v>
       </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="U10" t="n">
+        <v>0</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
       </c>
-      <c r="W10" t="n">
-        <v>0</v>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="X10" t="n">
         <v>0</v>
@@ -1529,8 +1498,10 @@
       <c r="Y10" t="n">
         <v>0</v>
       </c>
-      <c r="Z10" t="n">
-        <v>0</v>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1538,10 +1509,8 @@
       <c r="AB10" t="n">
         <v>0</v>
       </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AC10" t="n">
+        <v>0</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -1550,9 +1519,6 @@
         <v>0</v>
       </c>
       <c r="AF10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1594,42 +1560,42 @@
       <c r="K11" t="n">
         <v>0</v>
       </c>
-      <c r="L11" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" t="inlineStr">
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>0</v>
+      </c>
+      <c r="P11" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>0</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0</v>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="T11" t="n">
+        <v>0</v>
+      </c>
+      <c r="U11" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="O11" t="n">
-        <v>0</v>
-      </c>
-      <c r="P11" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q11" t="n">
-        <v>0</v>
-      </c>
-      <c r="R11" t="n">
-        <v>0</v>
-      </c>
-      <c r="S11" t="n">
-        <v>0</v>
-      </c>
-      <c r="T11" t="n">
-        <v>0</v>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
       <c r="V11" t="n">
         <v>0</v>
       </c>
@@ -1644,7 +1610,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="AA11" t="n">
@@ -1662,11 +1628,10 @@
       <c r="AE11" t="n">
         <v>0</v>
       </c>
-      <c r="AF11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
     </row>
     <row r="12">
@@ -1727,13 +1692,13 @@
       <c r="Q12" t="n">
         <v>0</v>
       </c>
-      <c r="R12" t="n">
-        <v>0</v>
-      </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="S12" t="n">
+        <v>0</v>
       </c>
       <c r="T12" t="inlineStr">
         <is>
@@ -1755,10 +1720,8 @@
       <c r="Y12" t="n">
         <v>0</v>
       </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
+      <c r="Z12" t="n">
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
         <v>0</v>
@@ -1766,8 +1729,10 @@
       <c r="AB12" t="n">
         <v>0</v>
       </c>
-      <c r="AC12" t="n">
-        <v>0</v>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AD12" t="n">
         <v>0</v>
@@ -1776,9 +1741,6 @@
         <v>0</v>
       </c>
       <c r="AF12" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1794,16 +1756,16 @@
       <c r="C13" t="n">
         <v>0</v>
       </c>
-      <c r="D13" t="n">
-        <v>0</v>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="F13" t="n">
+        <v>0</v>
       </c>
       <c r="G13" t="n">
         <v>0</v>
@@ -1814,10 +1776,8 @@
       <c r="I13" t="n">
         <v>0</v>
       </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="J13" t="n">
+        <v>0</v>
       </c>
       <c r="K13" t="n">
         <v>0</v>
@@ -1827,11 +1787,13 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="N13" t="n">
-        <v>0</v>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="N13" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="O13" t="n">
         <v>0</v>
@@ -1851,16 +1813,16 @@
       <c r="T13" t="n">
         <v>0</v>
       </c>
-      <c r="U13" t="n">
-        <v>0</v>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="V13" t="n">
         <v>0</v>
       </c>
-      <c r="W13" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="W13" t="n">
+        <v>0</v>
       </c>
       <c r="X13" t="n">
         <v>0</v>
@@ -1868,16 +1830,16 @@
       <c r="Y13" t="n">
         <v>0</v>
       </c>
-      <c r="Z13" t="n">
-        <v>0</v>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AA13" t="n">
         <v>0</v>
       </c>
-      <c r="AB13" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AB13" t="n">
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
         <v>0</v>
@@ -1889,9 +1851,6 @@
         <v>0</v>
       </c>
       <c r="AF13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG13" t="n">
         <v>0</v>
       </c>
     </row>
@@ -1927,16 +1886,16 @@
       <c r="I14" t="n">
         <v>0</v>
       </c>
-      <c r="J14" t="n">
-        <v>0</v>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="K14" t="n">
         <v>0</v>
       </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="L14" t="n">
+        <v>0</v>
       </c>
       <c r="M14" t="n">
         <v>0</v>
@@ -1963,7 +1922,7 @@
       </c>
       <c r="T14" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="U14" t="n">
@@ -2002,9 +1961,6 @@
         <v>0</v>
       </c>
       <c r="AF14" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG14" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2017,8 +1973,10 @@
       <c r="B15" t="n">
         <v>0</v>
       </c>
-      <c r="C15" t="n">
-        <v>0</v>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="D15" t="n">
         <v>0</v>
@@ -2029,10 +1987,8 @@
       <c r="F15" t="n">
         <v>0</v>
       </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="G15" t="n">
+        <v>0</v>
       </c>
       <c r="H15" t="n">
         <v>0</v>
@@ -2043,47 +1999,47 @@
       <c r="J15" t="n">
         <v>0</v>
       </c>
-      <c r="K15" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L15" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" t="n">
+        <v>0</v>
+      </c>
+      <c r="P15" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q15" t="n">
+        <v>0</v>
+      </c>
+      <c r="R15" t="n">
+        <v>0</v>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="M15" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" t="n">
-        <v>0</v>
-      </c>
-      <c r="P15" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="R15" t="n">
-        <v>0</v>
-      </c>
-      <c r="S15" t="n">
-        <v>0</v>
-      </c>
-      <c r="T15" t="n">
-        <v>0</v>
-      </c>
       <c r="U15" t="n">
         <v>0</v>
       </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="V15" t="n">
+        <v>0</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
@@ -2097,13 +2053,13 @@
       <c r="Z15" t="n">
         <v>0</v>
       </c>
-      <c r="AA15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="AB15" t="n">
+        <v>0</v>
       </c>
       <c r="AC15" t="n">
         <v>0</v>
@@ -2115,9 +2071,6 @@
         <v>0</v>
       </c>
       <c r="AF15" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG15" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2127,16 +2080,16 @@
           <t>ALYSSON GARCIA</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="B16" t="n">
+        <v>0</v>
       </c>
       <c r="C16" t="n">
         <v>0</v>
       </c>
-      <c r="D16" t="n">
-        <v>0</v>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="E16" t="n">
         <v>0</v>
@@ -2164,29 +2117,29 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="N16" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" t="n">
+        <v>0</v>
+      </c>
+      <c r="P16" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q16" t="n">
+        <v>0</v>
+      </c>
+      <c r="R16" t="n">
+        <v>0</v>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="N16" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" t="n">
-        <v>0</v>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="Q16" t="n">
-        <v>0</v>
-      </c>
-      <c r="R16" t="n">
-        <v>0</v>
-      </c>
-      <c r="S16" t="n">
-        <v>0</v>
-      </c>
       <c r="T16" t="n">
         <v>0</v>
       </c>
@@ -2195,7 +2148,7 @@
       </c>
       <c r="V16" t="inlineStr">
         <is>
-          <t>CM</t>
+          <t>NC</t>
         </is>
       </c>
       <c r="W16" t="n">
@@ -2207,13 +2160,13 @@
       <c r="Y16" t="n">
         <v>0</v>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="AA16" t="n">
-        <v>0</v>
+      <c r="Z16" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AB16" t="n">
         <v>0</v>
@@ -2221,18 +2174,13 @@
       <c r="AC16" t="n">
         <v>0</v>
       </c>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AD16" t="n">
+        <v>0</v>
       </c>
       <c r="AE16" t="n">
         <v>0</v>
       </c>
       <c r="AF16" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG16" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2242,8 +2190,10 @@
           <t>LUA DA ROCHA NOS</t>
         </is>
       </c>
-      <c r="B17" t="n">
-        <v>0</v>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="C17" t="n">
         <v>0</v>
@@ -2254,67 +2204,65 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" t="inlineStr">
+      <c r="F17" t="n">
+        <v>0</v>
+      </c>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="M17" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" t="n">
+        <v>0</v>
+      </c>
+      <c r="P17" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q17" t="n">
+        <v>0</v>
+      </c>
+      <c r="R17" t="n">
+        <v>0</v>
+      </c>
+      <c r="S17" t="n">
+        <v>0</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" t="n">
-        <v>0</v>
-      </c>
-      <c r="P17" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="R17" t="n">
-        <v>0</v>
-      </c>
-      <c r="S17" t="n">
-        <v>0</v>
-      </c>
-      <c r="T17" t="n">
-        <v>0</v>
-      </c>
-      <c r="U17" t="n">
-        <v>0</v>
-      </c>
       <c r="V17" t="n">
         <v>0</v>
       </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="W17" t="n">
+        <v>0</v>
       </c>
       <c r="X17" t="n">
         <v>0</v>
@@ -2322,14 +2270,14 @@
       <c r="Y17" t="n">
         <v>0</v>
       </c>
-      <c r="Z17" t="inlineStr">
+      <c r="Z17" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA17" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="AA17" t="n">
-        <v>0</v>
-      </c>
       <c r="AB17" t="n">
         <v>0</v>
       </c>
@@ -2345,9 +2293,6 @@
         <v>0</v>
       </c>
       <c r="AF17" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG17" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2368,7 +2313,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="F18" t="n">
@@ -2377,13 +2322,13 @@
       <c r="G18" t="n">
         <v>0</v>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="I18" t="n">
-        <v>0</v>
+      <c r="H18" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -2400,16 +2345,16 @@
       <c r="N18" t="n">
         <v>0</v>
       </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="O18" t="n">
+        <v>0</v>
       </c>
       <c r="P18" t="n">
         <v>0</v>
       </c>
-      <c r="Q18" t="n">
-        <v>0</v>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="R18" t="n">
         <v>0</v>
@@ -2417,16 +2362,16 @@
       <c r="S18" t="n">
         <v>0</v>
       </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="T18" t="n">
+        <v>0</v>
       </c>
       <c r="U18" t="n">
         <v>0</v>
       </c>
-      <c r="V18" t="n">
-        <v>0</v>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="W18" t="n">
         <v>0</v>
@@ -2440,16 +2385,16 @@
       <c r="Z18" t="n">
         <v>0</v>
       </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
+      <c r="AA18" t="n">
+        <v>0</v>
       </c>
       <c r="AB18" t="n">
         <v>0</v>
       </c>
-      <c r="AC18" t="n">
-        <v>0</v>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AD18" t="n">
         <v>0</v>
@@ -2457,12 +2402,7 @@
       <c r="AE18" t="n">
         <v>0</v>
       </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="AG18" t="n">
+      <c r="AF18" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2478,19 +2418,21 @@
       <c r="C19" t="n">
         <v>0</v>
       </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="D19" t="n">
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" t="n">
-        <v>0</v>
-      </c>
-      <c r="G19" t="n">
-        <v>0</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="H19" t="n">
         <v>0</v>
@@ -2504,61 +2446,59 @@
       <c r="K19" t="n">
         <v>0</v>
       </c>
-      <c r="L19" t="inlineStr">
+      <c r="L19" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" t="n">
+        <v>0</v>
+      </c>
+      <c r="P19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q19" t="n">
+        <v>0</v>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="S19" t="n">
+        <v>0</v>
+      </c>
+      <c r="T19" t="n">
+        <v>0</v>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="V19" t="n">
+        <v>0</v>
+      </c>
+      <c r="W19" t="n">
+        <v>0</v>
+      </c>
+      <c r="X19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y19" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z19" t="inlineStr">
         <is>
           <t>CV</t>
         </is>
       </c>
-      <c r="M19" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0</v>
-      </c>
-      <c r="P19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="R19" t="n">
-        <v>0</v>
-      </c>
-      <c r="S19" t="n">
-        <v>0</v>
-      </c>
-      <c r="T19" t="n">
-        <v>0</v>
-      </c>
-      <c r="U19" t="n">
-        <v>0</v>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="W19" t="n">
-        <v>0</v>
-      </c>
-      <c r="X19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y19" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AA19" t="n">
+        <v>0</v>
       </c>
       <c r="AB19" t="n">
         <v>0</v>
@@ -2573,9 +2513,6 @@
         <v>0</v>
       </c>
       <c r="AF19" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG19" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2591,13 +2528,13 @@
       <c r="C20" t="n">
         <v>0</v>
       </c>
-      <c r="D20" t="n">
-        <v>0</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>0</v>
       </c>
       <c r="F20" t="n">
         <v>0</v>
@@ -2611,13 +2548,13 @@
       <c r="I20" t="n">
         <v>0</v>
       </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K20" t="n">
-        <v>0</v>
+      <c r="J20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="L20" t="n">
         <v>0</v>
@@ -2640,38 +2577,38 @@
       <c r="R20" t="n">
         <v>0</v>
       </c>
-      <c r="S20" t="n">
-        <v>0</v>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="T20" t="inlineStr">
         <is>
           <t>NC</t>
         </is>
       </c>
-      <c r="U20" t="inlineStr">
+      <c r="U20" t="n">
+        <v>0</v>
+      </c>
+      <c r="V20" t="n">
+        <v>0</v>
+      </c>
+      <c r="W20" t="n">
+        <v>0</v>
+      </c>
+      <c r="X20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z20" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="V20" t="n">
-        <v>0</v>
-      </c>
-      <c r="W20" t="n">
-        <v>0</v>
-      </c>
-      <c r="X20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y20" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AA20" t="n">
+        <v>0</v>
       </c>
       <c r="AB20" t="n">
         <v>0</v>
@@ -2682,13 +2619,12 @@
       <c r="AD20" t="n">
         <v>0</v>
       </c>
-      <c r="AE20" t="n">
-        <v>0</v>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AF20" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG20" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2701,8 +2637,10 @@
       <c r="B21" t="n">
         <v>0</v>
       </c>
-      <c r="C21" t="n">
-        <v>0</v>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="D21" t="n">
         <v>0</v>
@@ -2710,72 +2648,68 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" t="inlineStr">
+      <c r="F21" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" t="n">
+        <v>0</v>
+      </c>
+      <c r="J21" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="N21" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" t="n">
+        <v>0</v>
+      </c>
+      <c r="P21" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q21" t="n">
+        <v>0</v>
+      </c>
+      <c r="R21" t="n">
+        <v>0</v>
+      </c>
+      <c r="S21" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="G21" t="n">
-        <v>0</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" t="n">
-        <v>0</v>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="K21" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="O21" t="n">
-        <v>0</v>
-      </c>
-      <c r="P21" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q21" t="n">
-        <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0</v>
-      </c>
-      <c r="S21" t="n">
-        <v>0</v>
-      </c>
       <c r="T21" t="n">
         <v>0</v>
       </c>
       <c r="U21" t="n">
         <v>0</v>
       </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="V21" t="n">
+        <v>0</v>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="X21" t="n">
+        <v>0</v>
       </c>
       <c r="Y21" t="n">
         <v>0</v>
@@ -2789,8 +2723,10 @@
       <c r="AB21" t="n">
         <v>0</v>
       </c>
-      <c r="AC21" t="n">
-        <v>0</v>
+      <c r="AC21" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AD21" t="n">
         <v>0</v>
@@ -2798,12 +2734,7 @@
       <c r="AE21" t="n">
         <v>0</v>
       </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
+      <c r="AF21" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2816,10 +2747,8 @@
       <c r="B22" t="n">
         <v>0</v>
       </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="C22" t="n">
+        <v>0</v>
       </c>
       <c r="D22" t="n">
         <v>0</v>
@@ -2827,14 +2756,18 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" t="n">
-        <v>0</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
-      <c r="H22" t="n">
-        <v>0</v>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="I22" t="n">
         <v>0</v>
@@ -2842,10 +2775,8 @@
       <c r="J22" t="n">
         <v>0</v>
       </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="K22" t="n">
+        <v>0</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2862,21 +2793,19 @@
       <c r="P22" t="n">
         <v>0</v>
       </c>
-      <c r="Q22" t="n">
-        <v>0</v>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="R22" t="n">
         <v>0</v>
       </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
+      <c r="S22" t="n">
+        <v>0</v>
+      </c>
+      <c r="T22" t="n">
+        <v>0</v>
       </c>
       <c r="U22" t="n">
         <v>0</v>
@@ -2887,8 +2816,10 @@
       <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="X22" t="n">
-        <v>0</v>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="Y22" t="n">
         <v>0</v>
@@ -2914,9 +2845,6 @@
         <v>0</v>
       </c>
       <c r="AF22" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG22" t="n">
         <v>0</v>
       </c>
     </row>
@@ -2932,13 +2860,13 @@
       <c r="C23" t="n">
         <v>0</v>
       </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="E23" t="n">
-        <v>0</v>
+      <c r="D23" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -2955,13 +2883,13 @@
       <c r="J23" t="n">
         <v>0</v>
       </c>
-      <c r="K23" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="L23" t="n">
+        <v>0</v>
       </c>
       <c r="M23" t="inlineStr">
         <is>
@@ -2989,13 +2917,13 @@
       <c r="T23" t="n">
         <v>0</v>
       </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="V23" t="n">
-        <v>0</v>
+      <c r="U23" t="n">
+        <v>0</v>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="W23" t="n">
         <v>0</v>
@@ -3003,16 +2931,16 @@
       <c r="X23" t="n">
         <v>0</v>
       </c>
-      <c r="Y23" t="n">
-        <v>0</v>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="Z23" t="n">
         <v>0</v>
       </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
+      <c r="AA23" t="n">
+        <v>0</v>
       </c>
       <c r="AB23" t="n">
         <v>0</v>
@@ -3023,13 +2951,12 @@
       <c r="AD23" t="n">
         <v>0</v>
       </c>
-      <c r="AE23" t="n">
-        <v>0</v>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AF23" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG23" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3042,8 +2969,10 @@
       <c r="B24" t="n">
         <v>0</v>
       </c>
-      <c r="C24" t="n">
-        <v>0</v>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="D24" t="n">
         <v>0</v>
@@ -3051,18 +2980,14 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>CM</t>
-        </is>
+      <c r="F24" t="n">
+        <v>0</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
-      <c r="H24" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="H24" t="n">
+        <v>0</v>
       </c>
       <c r="I24" t="n">
         <v>0</v>
@@ -3073,19 +2998,21 @@
       <c r="K24" t="n">
         <v>0</v>
       </c>
-      <c r="L24" t="n">
-        <v>0</v>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>CV</t>
+        </is>
       </c>
       <c r="M24" t="n">
         <v>0</v>
       </c>
-      <c r="N24" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>0</v>
       </c>
       <c r="P24" t="n">
         <v>0</v>
@@ -3140,9 +3067,6 @@
         <v>0</v>
       </c>
       <c r="AF24" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG24" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3155,16 +3079,16 @@
       <c r="B25" t="n">
         <v>0</v>
       </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="C25" t="n">
+        <v>0</v>
       </c>
       <c r="D25" t="n">
         <v>0</v>
       </c>
-      <c r="E25" t="n">
-        <v>0</v>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="F25" t="n">
         <v>0</v>
@@ -3181,13 +3105,13 @@
       <c r="J25" t="n">
         <v>0</v>
       </c>
-      <c r="K25" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="L25" t="n">
-        <v>0</v>
+      <c r="K25" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="M25" t="n">
         <v>0</v>
@@ -3207,17 +3131,17 @@
       <c r="R25" t="n">
         <v>0</v>
       </c>
-      <c r="S25" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="T25" t="n">
-        <v>0</v>
+      <c r="S25" t="n">
+        <v>0</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="U25" t="inlineStr">
         <is>
-          <t>CV</t>
+          <t>CM</t>
         </is>
       </c>
       <c r="V25" t="n">
@@ -3253,9 +3177,6 @@
         <v>0</v>
       </c>
       <c r="AF25" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG25" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3265,8 +3186,10 @@
           <t>RAFAEL ROCHA SOUZA</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>0</v>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="C26" t="n">
         <v>0</v>
@@ -3277,10 +3200,8 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="F26" t="n">
+        <v>0</v>
       </c>
       <c r="G26" t="n">
         <v>0</v>
@@ -3299,7 +3220,7 @@
       </c>
       <c r="L26" t="inlineStr">
         <is>
-          <t>NC</t>
+          <t>CV</t>
         </is>
       </c>
       <c r="M26" t="n">
@@ -3314,45 +3235,45 @@
       <c r="P26" t="n">
         <v>0</v>
       </c>
-      <c r="Q26" t="n">
-        <v>0</v>
-      </c>
-      <c r="R26" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="R26" t="n">
+        <v>0</v>
       </c>
       <c r="S26" t="n">
         <v>0</v>
       </c>
-      <c r="T26" t="inlineStr">
+      <c r="T26" t="n">
+        <v>0</v>
+      </c>
+      <c r="U26" t="n">
+        <v>0</v>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Y26" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z26" t="n">
+        <v>0</v>
+      </c>
+      <c r="AA26" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="U26" t="n">
-        <v>0</v>
-      </c>
-      <c r="V26" t="n">
-        <v>0</v>
-      </c>
-      <c r="W26" t="n">
-        <v>0</v>
-      </c>
-      <c r="X26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y26" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AA26" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
       <c r="AB26" t="n">
         <v>0</v>
       </c>
@@ -3362,15 +3283,10 @@
       <c r="AD26" t="n">
         <v>0</v>
       </c>
-      <c r="AE26" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="AE26" t="n">
+        <v>0</v>
       </c>
       <c r="AF26" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG26" t="n">
         <v>0</v>
       </c>
     </row>
@@ -3386,10 +3302,8 @@
       <c r="C27" t="n">
         <v>0</v>
       </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="D27" t="n">
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
@@ -3397,8 +3311,10 @@
       <c r="F27" t="n">
         <v>0</v>
       </c>
-      <c r="G27" t="n">
-        <v>0</v>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="H27" t="n">
         <v>0</v>
@@ -3412,16 +3328,18 @@
       <c r="K27" t="n">
         <v>0</v>
       </c>
-      <c r="L27" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="N27" t="n">
-        <v>0</v>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="M27" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="O27" t="n">
         <v>0</v>
@@ -3435,35 +3353,33 @@
       <c r="R27" t="n">
         <v>0</v>
       </c>
-      <c r="S27" t="inlineStr">
+      <c r="S27" t="n">
+        <v>0</v>
+      </c>
+      <c r="T27" t="n">
+        <v>0</v>
+      </c>
+      <c r="U27" t="n">
+        <v>0</v>
+      </c>
+      <c r="V27" t="inlineStr">
         <is>
           <t>CM</t>
         </is>
       </c>
-      <c r="T27" t="n">
-        <v>0</v>
-      </c>
-      <c r="U27" t="n">
-        <v>0</v>
-      </c>
-      <c r="V27" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
       <c r="W27" t="n">
         <v>0</v>
       </c>
-      <c r="X27" t="n">
-        <v>0</v>
+      <c r="X27" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="Y27" t="n">
         <v>0</v>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
+      <c r="Z27" t="n">
+        <v>0</v>
       </c>
       <c r="AA27" t="n">
         <v>0</v>
@@ -3480,11 +3396,10 @@
       <c r="AE27" t="n">
         <v>0</v>
       </c>
-      <c r="AF27" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG27" t="n">
-        <v>0</v>
+      <c r="AF27" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
     </row>
     <row r="28">
@@ -3502,21 +3417,21 @@
       <c r="D28" t="n">
         <v>0</v>
       </c>
-      <c r="E28" t="n">
-        <v>0</v>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>CV</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>CM</t>
+        </is>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -3556,8 +3471,10 @@
       <c r="T28" t="n">
         <v>0</v>
       </c>
-      <c r="U28" t="n">
-        <v>0</v>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="V28" t="n">
         <v>0</v>
@@ -3565,10 +3482,8 @@
       <c r="W28" t="n">
         <v>0</v>
       </c>
-      <c r="X28" t="inlineStr">
-        <is>
-          <t>NC</t>
-        </is>
+      <c r="X28" t="n">
+        <v>0</v>
       </c>
       <c r="Y28" t="n">
         <v>0</v>
@@ -3587,16 +3502,15 @@
       <c r="AC28" t="n">
         <v>0</v>
       </c>
-      <c r="AD28" t="n">
-        <v>0</v>
+      <c r="AD28" t="inlineStr">
+        <is>
+          <t>NC</t>
+        </is>
       </c>
       <c r="AE28" t="n">
         <v>0</v>
       </c>
       <c r="AF28" t="n">
-        <v>0</v>
-      </c>
-      <c r="AG28" t="n">
         <v>0</v>
       </c>
     </row>
